--- a/final_outputs/excel_tables/table_qlp_subsamples_summary.xlsx
+++ b/final_outputs/excel_tables/table_qlp_subsamples_summary.xlsx
@@ -749,12 +749,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h1-q0.90</t>
+          <t>None</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Significant responses present at listed horizon-quantile pairs.</t>
+          <t>No significant dynamic responses.</t>
         </is>
       </c>
     </row>
@@ -771,12 +771,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h5-q0.50</t>
+          <t>None</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Significant responses present at listed horizon-quantile pairs.</t>
+          <t>No significant dynamic responses.</t>
         </is>
       </c>
     </row>
